--- a/data/trans_orig/Q5409-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5409-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la orina (incontinencia) en 2007</t>
+          <t>Población según si se le escapa la orina (incontinencia) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12705</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>12537</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31108</t>
+          <t>31760</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17828</t>
+          <t>17303</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39638</t>
+          <t>39321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15862</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33779</t>
+          <t>33773</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26156</t>
+          <t>26069</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51584</t>
+          <t>51962</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47678</t>
+          <t>48264</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77063</t>
+          <t>78103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>331071</t>
+          <t>333525</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>352352</t>
+          <t>352323</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>514328</t>
+          <t>512252</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>543585</t>
+          <t>543337</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>854160</t>
+          <t>853560</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>889361</t>
+          <t>889440</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -1189,97 +1189,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1875</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5762</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5663</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6655</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6801</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9486</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12636</t>
+          <t>12964</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78597</t>
+          <t>78776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86454</t>
+          <t>86458</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52433</t>
+          <t>52434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61106</t>
+          <t>61082</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>136249</t>
+          <t>135356</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147030</t>
+          <t>146708</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1758,97 +1758,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12196</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31831</t>
+          <t>31630</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17577</t>
+          <t>18966</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38891</t>
+          <t>39323</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39200</t>
+          <t>38076</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29399</t>
+          <t>29389</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55089</t>
+          <t>54812</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52658</t>
+          <t>52963</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>85466</t>
+          <t>84314</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>456411</t>
+          <t>458017</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>477807</t>
+          <t>478159</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>598254</t>
+          <t>599640</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>628518</t>
+          <t>629432</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1064700</t>
+          <t>1063421</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1101847</t>
+          <t>1100308</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la orina (incontinencia) en 2012</t>
+          <t>Población según si se le escapa la orina (incontinencia) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29687</t>
+          <t>29958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56293</t>
+          <t>55437</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34889</t>
+          <t>35136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64113</t>
+          <t>62634</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29118</t>
+          <t>29901</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58142</t>
+          <t>57309</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52023</t>
+          <t>52640</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83711</t>
+          <t>85046</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85986</t>
+          <t>90574</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>130290</t>
+          <t>131536</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>349504</t>
+          <t>348918</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>379271</t>
+          <t>378517</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>507758</t>
+          <t>504770</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>546045</t>
+          <t>545563</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>865048</t>
+          <t>867788</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>916367</t>
+          <t>914157</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,15%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>9316</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8947</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14010</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106687</t>
+          <t>106795</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116605</t>
+          <t>116700</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69166</t>
+          <t>69180</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79560</t>
+          <t>80098</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>179518</t>
+          <t>180650</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194822</t>
+          <t>194519</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -3700,97 +3700,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1162</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6242</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>28,06%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>1162</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6061</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>5892</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>27,24%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1162</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>6351</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -3813,97 +3813,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2161</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6537</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>9,72%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>29,39%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>2161</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6935</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,72%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6730</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>31,18%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2161</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>7879</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24279</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14122</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21282</t>
+          <t>21242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39571</t>
+          <t>40052</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47855</t>
+          <t>47838</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32430</t>
+          <t>32482</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>59317</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41281</t>
+          <t>41297</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72288</t>
+          <t>71708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31083</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61605</t>
+          <t>59091</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57412</t>
+          <t>57785</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90710</t>
+          <t>90208</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>93804</t>
+          <t>98166</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140375</t>
+          <t>143589</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>486674</t>
+          <t>490906</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>519142</t>
+          <t>521194</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>601534</t>
+          <t>600159</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>642804</t>
+          <t>640148</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1099546</t>
+          <t>1100588</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1151281</t>
+          <t>1153086</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,73%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la orina (incontinencia) en 2016</t>
+          <t>Población según si se le escapa la orina (incontinencia) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>14868</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19794</t>
+          <t>20756</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44815</t>
+          <t>45022</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27180</t>
+          <t>26015</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55512</t>
+          <t>52127</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22603</t>
+          <t>22011</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42574</t>
+          <t>42545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50428</t>
+          <t>49584</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83810</t>
+          <t>81634</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79735</t>
+          <t>79116</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116779</t>
+          <t>117269</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>302756</t>
+          <t>302675</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>325028</t>
+          <t>325569</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>440540</t>
+          <t>440748</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>478721</t>
+          <t>477686</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>749370</t>
+          <t>750111</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>795520</t>
+          <t>794044</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,39%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15232</t>
+          <t>14196</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>10535</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26365</t>
+          <t>26452</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>177280</t>
+          <t>177171</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>188770</t>
+          <t>188398</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>166078</t>
+          <t>165478</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>180577</t>
+          <t>180015</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>348599</t>
+          <t>349079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>366880</t>
+          <t>366765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -5755,97 +5755,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8575</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33454</t>
+          <t>33343</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24313</t>
+          <t>23164</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33674</t>
+          <t>32632</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63505</t>
+          <t>61971</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74320</t>
+          <t>74343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14460</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23023</t>
+          <t>23007</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48116</t>
+          <t>48803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>30951</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58182</t>
+          <t>59114</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30673</t>
+          <t>30370</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53657</t>
+          <t>54692</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61320</t>
+          <t>61393</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96923</t>
+          <t>97273</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97354</t>
+          <t>98575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139722</t>
+          <t>142934</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>525201</t>
+          <t>523286</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>549837</t>
+          <t>550437</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>642130</t>
+          <t>641970</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>684049</t>
+          <t>684227</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1179026</t>
+          <t>1174339</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1227040</t>
+          <t>1225970</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la orina (incontinencia) en 2023</t>
+          <t>Población según si se le escapa la orina (incontinencia) en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7469</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17090</t>
+          <t>17431</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>26182</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43316</t>
+          <t>42997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36639</t>
+          <t>37618</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56338</t>
+          <t>56036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>17891</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31817</t>
+          <t>33079</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57631</t>
+          <t>57321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78914</t>
+          <t>79520</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79628</t>
+          <t>79454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105883</t>
+          <t>105415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>222788</t>
+          <t>222852</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>240639</t>
+          <t>240466</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>384947</t>
+          <t>384780</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>409277</t>
+          <t>410870</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>615748</t>
+          <t>614472</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>645592</t>
+          <t>644059</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,84%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>944</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9969</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16111</t>
+          <t>16088</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30385</t>
+          <t>30506</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43100</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19799</t>
+          <t>20011</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>66249</t>
+          <t>65081</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>237985</t>
+          <t>237565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>253245</t>
+          <t>253456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>403811</t>
+          <t>405123</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>447596</t>
+          <t>447004</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>649942</t>
+          <t>652318</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>704518</t>
+          <t>706008</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10371</t>
+          <t>10868</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>11376</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18759</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93726</t>
+          <t>93616</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101755</t>
+          <t>101951</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59288</t>
+          <t>59132</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66933</t>
+          <t>66708</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155337</t>
+          <t>155787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166861</t>
+          <t>166990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>11448</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23776</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19612</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53611</t>
+          <t>52305</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37313</t>
+          <t>35295</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71328</t>
+          <t>69662</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42299</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63765</t>
+          <t>63484</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50726</t>
+          <t>51062</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124909</t>
+          <t>126201</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>96454</t>
+          <t>94343</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>174207</t>
+          <t>176539</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>564918</t>
+          <t>565086</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>588719</t>
+          <t>589165</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>851949</t>
+          <t>852772</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>954862</t>
+          <t>953847</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1433405</t>
+          <t>1433060</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1538222</t>
+          <t>1544201</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5409-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5409-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11342</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>12300</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31760</t>
+          <t>30365</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17303</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39321</t>
+          <t>37503</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33773</t>
+          <t>34685</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26069</t>
+          <t>27326</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51962</t>
+          <t>51628</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48264</t>
+          <t>49199</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78103</t>
+          <t>79256</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>333525</t>
+          <t>331520</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>352323</t>
+          <t>351810</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>512252</t>
+          <t>513314</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>543337</t>
+          <t>543023</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>853560</t>
+          <t>853183</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>889440</t>
+          <t>889104</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>13909</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78776</t>
+          <t>79799</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86458</t>
+          <t>86475</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52434</t>
+          <t>52849</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61082</t>
+          <t>61106</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135356</t>
+          <t>135093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146708</t>
+          <t>147333</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11344</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31630</t>
+          <t>33402</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39323</t>
+          <t>40036</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>19910</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38076</t>
+          <t>38990</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29389</t>
+          <t>28881</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54812</t>
+          <t>54270</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52963</t>
+          <t>52213</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>84314</t>
+          <t>84147</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>458017</t>
+          <t>456812</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>478159</t>
+          <t>478663</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>599640</t>
+          <t>597355</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>629432</t>
+          <t>629313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1063421</t>
+          <t>1064970</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1100308</t>
+          <t>1102781</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13898</t>
+          <t>13924</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29958</t>
+          <t>28874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55437</t>
+          <t>54789</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35136</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62634</t>
+          <t>64131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29901</t>
+          <t>28678</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57309</t>
+          <t>57198</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52640</t>
+          <t>51800</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85046</t>
+          <t>83373</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90574</t>
+          <t>88335</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131536</t>
+          <t>132277</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>348918</t>
+          <t>350063</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>378517</t>
+          <t>379851</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>504770</t>
+          <t>507471</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>545563</t>
+          <t>546799</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>867788</t>
+          <t>866781</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>914157</t>
+          <t>917977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11710</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106795</t>
+          <t>106796</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116700</t>
+          <t>116560</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69180</t>
+          <t>68129</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80098</t>
+          <t>79897</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>180650</t>
+          <t>180726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194519</t>
+          <t>194602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>21239</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40052</t>
+          <t>39930</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47838</t>
+          <t>47808</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>17561</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32482</t>
+          <t>33290</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59317</t>
+          <t>59929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41297</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71708</t>
+          <t>71877</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29896</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59091</t>
+          <t>61720</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57785</t>
+          <t>57415</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90208</t>
+          <t>90216</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>98166</t>
+          <t>96002</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>143589</t>
+          <t>140671</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>490906</t>
+          <t>488107</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>521194</t>
+          <t>518090</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>600159</t>
+          <t>600184</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>640148</t>
+          <t>640880</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1100588</t>
+          <t>1100063</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1153086</t>
+          <t>1150152</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14868</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20756</t>
+          <t>18735</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45022</t>
+          <t>44401</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26015</t>
+          <t>26692</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52127</t>
+          <t>51237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22011</t>
+          <t>22997</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42545</t>
+          <t>43069</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49584</t>
+          <t>48938</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81634</t>
+          <t>82615</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79116</t>
+          <t>78033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117269</t>
+          <t>116660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>302675</t>
+          <t>301701</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>325569</t>
+          <t>324165</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>440748</t>
+          <t>437929</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>477686</t>
+          <t>477889</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>750111</t>
+          <t>748298</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>794044</t>
+          <t>793599</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,34%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10448</t>
+          <t>10443</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14196</t>
+          <t>13753</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17262</t>
+          <t>17457</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10535</t>
+          <t>10668</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26452</t>
+          <t>27363</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>177171</t>
+          <t>177752</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>188398</t>
+          <t>189177</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165478</t>
+          <t>164744</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>180015</t>
+          <t>180378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>349079</t>
+          <t>347460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>366765</t>
+          <t>365600</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8686</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13732</t>
+          <t>13008</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>33221</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23164</t>
+          <t>23337</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32632</t>
+          <t>32603</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61971</t>
+          <t>62695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74343</t>
+          <t>74285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15692</t>
+          <t>16688</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23007</t>
+          <t>23517</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48803</t>
+          <t>49147</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30951</t>
+          <t>30991</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59114</t>
+          <t>59562</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30370</t>
+          <t>29628</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54692</t>
+          <t>52798</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61393</t>
+          <t>61728</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>97273</t>
+          <t>98676</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>98575</t>
+          <t>99985</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142934</t>
+          <t>144353</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>523286</t>
+          <t>526290</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>550437</t>
+          <t>550286</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>641970</t>
+          <t>642487</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>684227</t>
+          <t>685553</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1174339</t>
+          <t>1173870</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1225970</t>
+          <t>1226303</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11955</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17431</t>
+          <t>18235</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34128</t>
+          <t>38291</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26182</t>
+          <t>30180</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42997</t>
+          <t>48373</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>46083</t>
+          <t>50541</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37618</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56036</t>
+          <t>61686</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24070</t>
+          <t>26153</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17891</t>
+          <t>18399</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33079</t>
+          <t>35460</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67408</t>
+          <t>73376</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57321</t>
+          <t>62996</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79520</t>
+          <t>86010</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>91478</t>
+          <t>99529</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79454</t>
+          <t>85731</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105415</t>
+          <t>114116</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>232615</t>
+          <t>251039</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>222852</t>
+          <t>241043</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>240466</t>
+          <t>259656</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>398052</t>
+          <t>425890</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>384780</t>
+          <t>412278</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>410870</t>
+          <t>439638</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>630667</t>
+          <t>676930</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>614472</t>
+          <t>658562</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>644059</t>
+          <t>693460</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>268639</t>
+          <t>289442</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>268639</t>
+          <t>289442</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>268639</t>
+          <t>289442</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>499589</t>
+          <t>537557</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>499589</t>
+          <t>537557</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>499589</t>
+          <t>537557</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>768228</t>
+          <t>827000</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>768228</t>
+          <t>827000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>768228</t>
+          <t>827000</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,22 +7349,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>9694</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14644</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22379</t>
+          <t>23997</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30506</t>
+          <t>31825</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21287</t>
+          <t>23772</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>17706</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42681</t>
+          <t>31370</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>43666</t>
+          <t>47769</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20011</t>
+          <t>38108</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>65081</t>
+          <t>59582</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>246670</t>
+          <t>275252</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>237565</t>
+          <t>265753</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>253456</t>
+          <t>282671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>430214</t>
+          <t>248878</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>405123</t>
+          <t>240032</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>447004</t>
+          <t>255874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>676883</t>
+          <t>524130</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>652318</t>
+          <t>511001</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>706008</t>
+          <t>534002</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>868</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7815,12 +7815,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>748</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>13320</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11376</t>
+          <t>13359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>12909</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18551</t>
+          <t>22944</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>98612</t>
+          <t>110281</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93616</t>
+          <t>104292</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101951</t>
+          <t>114311</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>63436</t>
+          <t>73850</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59132</t>
+          <t>68396</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66708</t>
+          <t>77374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>162048</t>
+          <t>184131</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155787</t>
+          <t>177065</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166990</t>
+          <t>189872</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>12487</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>25782</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>39019</t>
+          <t>44035</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>35641</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52305</t>
+          <t>55571</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>55884</t>
+          <t>61729</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35295</t>
+          <t>50389</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69662</t>
+          <t>74672</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52121</t>
+          <t>57882</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41308</t>
+          <t>46509</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63484</t>
+          <t>71290</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>95932</t>
+          <t>105405</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>92023</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126201</t>
+          <t>119581</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>148053</t>
+          <t>163287</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>94343</t>
+          <t>144989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176539</t>
+          <t>182353</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>577896</t>
+          <t>636573</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>565086</t>
+          <t>621383</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>589165</t>
+          <t>649874</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>891702</t>
+          <t>748618</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>852772</t>
+          <t>731915</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>953847</t>
+          <t>763766</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1469598</t>
+          <t>1385190</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1433060</t>
+          <t>1363564</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1544201</t>
+          <t>1407644</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>87,42%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>646882</t>
+          <t>712149</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>646882</t>
+          <t>712149</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>646882</t>
+          <t>712149</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1026653</t>
+          <t>898058</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1026653</t>
+          <t>898058</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1026653</t>
+          <t>898058</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1673535</t>
+          <t>1610207</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1673535</t>
+          <t>1610207</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1673535</t>
+          <t>1610207</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
